--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2018_o_higgins.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:25</t>
+    <t xml:space="preserve">2026-09-09 20:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2018_o_higgins.xlsx
@@ -24,102 +24,102 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Rancagua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coinco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coltauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doñihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graneros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Cabras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malloa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostazal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peumo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichidegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta de Tilcoco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rengo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requínoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Vicente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichilemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Estrella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litueche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paredones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fernando</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chépica</t>
   </si>
   <si>
     <t xml:space="preserve">Chimbarongo</t>
   </si>
   <si>
-    <t xml:space="preserve">Codegua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coinco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coltauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doñihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graneros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Estrella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Cabras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Litueche</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
-    <t xml:space="preserve">Machalí</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malloa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marchihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mostazal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nancagua</t>
   </si>
   <si>
-    <t xml:space="preserve">Navidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Palmilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Paredones</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peralillo</t>
   </si>
   <si>
-    <t xml:space="preserve">Peumo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichidegua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichilemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Placilla</t>
   </si>
   <si>
     <t xml:space="preserve">Pumanque</t>
   </si>
   <si>
-    <t xml:space="preserve">Quinta de Tilcoco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rancagua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rengo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requínoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Fernando</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Vicente</t>
-  </si>
-  <si>
     <t xml:space="preserve">Santa Cruz</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:22</t>
+    <t xml:space="preserve">2026-09-18 10:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.54</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6.69</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.57</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="5">
@@ -568,7 +568,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.62</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.59</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="7">
@@ -584,7 +584,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.57</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="8">
@@ -592,7 +592,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.66</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="9">
@@ -600,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5.4</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.83</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="11">
@@ -616,7 +616,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7.17</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>5</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="13">
@@ -632,7 +632,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4.05</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="14">
@@ -640,7 +640,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5.21</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="15">
@@ -648,7 +648,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>6.38</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="16">
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>6.03</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="17">
@@ -664,7 +664,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5.01</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="18">
@@ -672,7 +672,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7.28</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="19">
@@ -680,7 +680,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>6.77</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="20">
@@ -688,7 +688,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="21">
@@ -696,7 +696,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>5.85</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="22">
@@ -704,7 +704,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.02</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="23">
@@ -712,7 +712,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7.58</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="24">
@@ -720,7 +720,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3.49</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="25">
@@ -728,7 +728,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>5.04</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="26">
@@ -736,7 +736,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4.89</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="27">
@@ -744,7 +744,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>4.43</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="28">
@@ -752,7 +752,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -760,7 +760,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>5.69</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="30">
@@ -768,7 +768,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>6.16</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="31">
@@ -776,7 +776,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>4.54</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="32">
@@ -784,7 +784,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>6.47</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="33">
@@ -792,7 +792,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>5.34</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="34">
